--- a/client-social-directory.xlsx
+++ b/client-social-directory.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Legend" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Client Directory'!$A$1:$Q$25</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Client Directory'!$A$1:$R$40</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -110,7 +110,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -141,6 +141,9 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -233,167 +236,252 @@
     <author>Claude</author>
   </authors>
   <commentList>
-    <comment ref="L2" authorId="0" shapeId="0">
+    <comment ref="M2" authorId="0" shapeId="0">
       <text>
         <t>UNVERIFIED: Google Maps search link for 'ADAMS Wereldkeuken Sierenborch 10d Amsterdam'. Open it, confirm the listing, and replace it with the listing's share link.</t>
       </text>
     </comment>
-    <comment ref="H3" authorId="0" shapeId="0">
+    <comment ref="I3" authorId="0" shapeId="0">
       <text>
         <t>UNVERIFIED: This is a personal LinkedIn profile named 'Anno Asia', not a company page</t>
       </text>
     </comment>
-    <comment ref="L3" authorId="0" shapeId="0">
+    <comment ref="M3" authorId="0" shapeId="0">
       <text>
         <t>UNVERIFIED: Google Maps search link for 'Anno Asia Julianaplein 47 Amsterdam'. Open it, confirm the listing, and replace it with the listing's share link.</t>
       </text>
     </comment>
-    <comment ref="G4" authorId="0" shapeId="0">
+    <comment ref="H4" authorId="0" shapeId="0">
       <text>
         <t>UNVERIFIED: Personal-style profile, not a business page; name match only</t>
       </text>
     </comment>
-    <comment ref="H4" authorId="0" shapeId="0">
+    <comment ref="I4" authorId="0" shapeId="0">
       <text>
         <t>UNVERIFIED: Personal LinkedIn profile, not a company page</t>
       </text>
     </comment>
-    <comment ref="L4" authorId="0" shapeId="0">
+    <comment ref="M4" authorId="0" shapeId="0">
       <text>
         <t>UNVERIFIED: Google Maps search link for 'Deni Stukadoor Amsterdam'. Open it, confirm the listing, and replace it with the listing's share link.</t>
       </text>
     </comment>
-    <comment ref="F5" authorId="0" shapeId="0">
+    <comment ref="G5" authorId="0" shapeId="0">
       <text>
         <t>UNVERIFIED: Two IG accounts found: @copyshop_vd_heijden and @drukkerijvanderheijden. Confirm which one is active</t>
       </text>
     </comment>
-    <comment ref="L5" authorId="0" shapeId="0">
+    <comment ref="M5" authorId="0" shapeId="0">
       <text>
         <t>UNVERIFIED: Google Maps search link for 'Drukkerij Copyshop van der Heijden 's-Hertogenbosch'. Open it, confirm the listing, and replace it with the listing's share link.</t>
       </text>
     </comment>
-    <comment ref="L6" authorId="0" shapeId="0">
+    <comment ref="M6" authorId="0" shapeId="0">
       <text>
         <t>UNVERIFIED: Address differs between sources (Waardenburg / Bruchem). Google Maps search link for 'Elmaas schuifpuien Waardenburg'. Open it, confirm the listing, and replace it with the listing's share link.</t>
       </text>
     </comment>
-    <comment ref="L7" authorId="0" shapeId="0">
+    <comment ref="M7" authorId="0" shapeId="0">
       <text>
         <t>UNVERIFIED: Google Maps search link for 'Fire Defence Leonardo da Vinciplein 76 Haarlem'. Open it, confirm the listing, and replace it with the listing's share link.</t>
       </text>
     </comment>
-    <comment ref="K8" authorId="0" shapeId="0">
+    <comment ref="L8" authorId="0" shapeId="0">
       <text>
         <t>UNVERIFIED: Channel handle looks auto-generated; confirm it is the official channel</t>
       </text>
     </comment>
-    <comment ref="L8" authorId="0" shapeId="0">
+    <comment ref="M8" authorId="0" shapeId="0">
       <text>
         <t>UNVERIFIED: Google Maps search link for 'Foodhall Scheveningen'. Open it, confirm the listing, and replace it with the listing's share link.</t>
       </text>
     </comment>
-    <comment ref="E9" authorId="0" shapeId="0">
+    <comment ref="F9" authorId="0" shapeId="0">
       <text>
         <t>UNVERIFIED: Two X accounts found: @GenkiGarden and @RestaurantGenki. Confirm which is theirs</t>
       </text>
     </comment>
-    <comment ref="L9" authorId="0" shapeId="0">
+    <comment ref="M9" authorId="0" shapeId="0">
       <text>
         <t>UNVERIFIED: Google Maps search link for 'Genki Garden Reguliersdwarsstraat 26 Amsterdam'. Open it, confirm the listing, and replace it with the listing's share link.</t>
       </text>
     </comment>
-    <comment ref="L10" authorId="0" shapeId="0">
+    <comment ref="M10" authorId="0" shapeId="0">
       <text>
         <t>UNVERIFIED: Google Maps search link for 'Glasservice Noord Spanjaardwaard 43 's-Hertogenbosch'. Open it, confirm the listing, and replace it with the listing's share link.</t>
       </text>
     </comment>
-    <comment ref="E11" authorId="0" shapeId="0">
+    <comment ref="F11" authorId="0" shapeId="0">
       <text>
         <t>UNVERIFIED: Name match only; could be an unrelated account</t>
       </text>
     </comment>
-    <comment ref="K11" authorId="0" shapeId="0">
+    <comment ref="L11" authorId="0" shapeId="0">
       <text>
         <t>UNVERIFIED: Name match only; could be an unrelated account</t>
       </text>
     </comment>
-    <comment ref="L11" authorId="0" shapeId="0">
+    <comment ref="M11" authorId="0" shapeId="0">
       <text>
         <t>UNVERIFIED: Google Maps search link for 'Hotspot Fishing Rijpwetering'. Open it, confirm the listing, and replace it with the listing's share link.</t>
       </text>
     </comment>
-    <comment ref="L12" authorId="0" shapeId="0">
+    <comment ref="M12" authorId="0" shapeId="0">
       <text>
         <t>UNVERIFIED: Google Maps search link for 'Just Dai Koningin Wilhelminaplein 13 Amsterdam'. Open it, confirm the listing, and replace it with the listing's share link.</t>
       </text>
     </comment>
-    <comment ref="L13" authorId="0" shapeId="0">
+    <comment ref="M13" authorId="0" shapeId="0">
+      <text>
+        <t>UNVERIFIED: Google Maps search link for 'L'albero Leidsekruisstraat 30 Amsterdam'. Open it, confirm the listing, and replace it with the listing's share link.</t>
+      </text>
+    </comment>
+    <comment ref="M14" authorId="0" shapeId="0">
       <text>
         <t>UNVERIFIED: Google Maps search link for 'Landgoed Groenendaal Groenendaal 3 Heemstede'. Open it, confirm the listing, and replace it with the listing's share link.</t>
       </text>
     </comment>
-    <comment ref="L14" authorId="0" shapeId="0">
+    <comment ref="M15" authorId="0" shapeId="0">
       <text>
         <t>UNVERIFIED: Google Maps search link for 'Madam Chen Kolk 50B Rotterdam'. Open it, confirm the listing, and replace it with the listing's share link.</t>
       </text>
     </comment>
-    <comment ref="L15" authorId="0" shapeId="0">
+    <comment ref="M16" authorId="0" shapeId="0">
       <text>
         <t>UNVERIFIED: Google Maps search link for 'Oran Aesthetics Arent Janszoon Ernststraat Amsterdam'. Open it, confirm the listing, and replace it with the listing's share link.</t>
       </text>
     </comment>
-    <comment ref="L16" authorId="0" shapeId="0">
+    <comment ref="M17" authorId="0" shapeId="0">
       <text>
         <t>UNVERIFIED: Google Maps search link for 'Wokrestaurant Oriental Langelaan 2a Noordwijkerhout'. Open it, confirm the listing, and replace it with the listing's share link.</t>
       </text>
     </comment>
-    <comment ref="L17" authorId="0" shapeId="0">
+    <comment ref="M19" authorId="0" shapeId="0">
+      <text>
+        <t>UNVERIFIED: Google Maps search link for 'Pad Thai Berenstraat 20H Amsterdam'. Open it, confirm the listing, and replace it with the listing's share link.</t>
+      </text>
+    </comment>
+    <comment ref="M20" authorId="0" shapeId="0">
+      <text>
+        <t>UNVERIFIED: Google Maps search link for 'Pad Thai Kinkerstraat 142 Amsterdam'. Open it, confirm the listing, and replace it with the listing's share link.</t>
+      </text>
+    </comment>
+    <comment ref="M21" authorId="0" shapeId="0">
+      <text>
+        <t>UNVERIFIED: Google Maps search link for 'Pad Thai Zeedijk 119 Amsterdam'. Open it, confirm the listing, and replace it with the listing's share link.</t>
+      </text>
+    </comment>
+    <comment ref="M22" authorId="0" shapeId="0">
+      <text>
+        <t>UNVERIFIED: Google Maps search link for 'Pad Thai Noordeinde 13 Den Haag'. Open it, confirm the listing, and replace it with the listing's share link.</t>
+      </text>
+    </comment>
+    <comment ref="M23" authorId="0" shapeId="0">
+      <text>
+        <t>UNVERIFIED: Google Maps search link for 'Pad Thai Westfield Mall Kornoelje 119 Leidschendam'. Open it, confirm the listing, and replace it with the listing's share link.</t>
+      </text>
+    </comment>
+    <comment ref="M24" authorId="0" shapeId="0">
+      <text>
+        <t>UNVERIFIED: Utrecht opening was announced on Facebook but no address was found. Google Maps search link for 'Pad Thai World Utrecht'. Open it, confirm the listing, and replace it with the listing's share link.</t>
+      </text>
+    </comment>
+    <comment ref="M25" authorId="0" shapeId="0">
+      <text>
+        <t>UNVERIFIED: Google Maps search link for 'Peppino Leidsekruisstraat 32 Amsterdam'. Open it, confirm the listing, and replace it with the listing's share link.</t>
+      </text>
+    </comment>
+    <comment ref="M26" authorId="0" shapeId="0">
       <text>
         <t>UNVERIFIED: Google Maps search link for 'Restaurant ChouChou Strandweg 159 Den Haag'. Open it, confirm the listing, and replace it with the listing's share link.</t>
       </text>
     </comment>
-    <comment ref="L18" authorId="0" shapeId="0">
+    <comment ref="M27" authorId="0" shapeId="0">
       <text>
         <t>UNVERIFIED: Google Maps search link for 'De Gouden Wok Zuiderpark Den Haag'. Open it, confirm the listing, and replace it with the listing's share link.</t>
       </text>
     </comment>
-    <comment ref="L19" authorId="0" shapeId="0">
+    <comment ref="M28" authorId="0" shapeId="0">
       <text>
         <t>UNVERIFIED: Google Maps search link for 'Guru Restaurant Rijnstraat 157 Amsterdam'. Open it, confirm the listing, and replace it with the listing's share link.</t>
       </text>
     </comment>
-    <comment ref="L20" authorId="0" shapeId="0">
+    <comment ref="M29" authorId="0" shapeId="0">
       <text>
         <t>UNVERIFIED: Google Maps search link for 'Restaurant Lavash Korte Leidsedwarsstraat 119 Amsterdam'. Open it, confirm the listing, and replace it with the listing's share link.</t>
       </text>
     </comment>
-    <comment ref="F21" authorId="0" shapeId="0">
+    <comment ref="H30" authorId="0" shapeId="0">
+      <text>
+        <t>UNVERIFIED: No separate Facebook page found for this branch; the 'Restaurant MIDO Zeist' page posts for all branches</t>
+      </text>
+    </comment>
+    <comment ref="M30" authorId="0" shapeId="0">
+      <text>
+        <t>UNVERIFIED: Google Maps search link for 'Restaurant MIDO Soestdijkerstraatweg 42A Hilversum'. Open it, confirm the listing, and replace it with the listing's share link.</t>
+      </text>
+    </comment>
+    <comment ref="H31" authorId="0" shapeId="0">
+      <text>
+        <t>UNVERIFIED: No separate Facebook page found for this branch; the 'Restaurant MIDO Zeist' page posts for all branches</t>
+      </text>
+    </comment>
+    <comment ref="M31" authorId="0" shapeId="0">
+      <text>
+        <t>UNVERIFIED: Google Maps search link for 'MIDO Heereweg 10 Lisse'. Open it, confirm the listing, and replace it with the listing's share link.</t>
+      </text>
+    </comment>
+    <comment ref="H32" authorId="0" shapeId="0">
+      <text>
+        <t>UNVERIFIED: No separate Facebook page found for this branch; the 'Restaurant MIDO Zeist' page posts for all branches</t>
+      </text>
+    </comment>
+    <comment ref="M32" authorId="0" shapeId="0">
+      <text>
+        <t>UNVERIFIED: Google Maps search link for 'Restaurant MIDO Woerden'. Open it, confirm the listing, and replace it with the listing's share link.</t>
+      </text>
+    </comment>
+    <comment ref="M33" authorId="0" shapeId="0">
+      <text>
+        <t>UNVERIFIED: Google Maps search link for 'Restaurant MIDO Het Rond 5 Zeist'. Open it, confirm the listing, and replace it with the listing's share link.</t>
+      </text>
+    </comment>
+    <comment ref="G34" authorId="0" shapeId="0">
       <text>
         <t>UNVERIFIED: Handle inferred from a post; profile not confirmed</t>
       </text>
     </comment>
-    <comment ref="L21" authorId="0" shapeId="0">
+    <comment ref="M34" authorId="0" shapeId="0">
       <text>
         <t>UNVERIFIED: Online drafting service; may not have a Google Business profile. Google Maps search link for 'SK Tekenwerk'. Open it, confirm the listing, and replace it with the listing's share link.</t>
       </text>
     </comment>
-    <comment ref="L22" authorId="0" shapeId="0">
+    <comment ref="M35" authorId="0" shapeId="0">
       <text>
         <t>UNVERIFIED: Google Maps search link for 'SOMEHO Cruquiuszoom 55 Cruquius'. Open it, confirm the listing, and replace it with the listing's share link.</t>
       </text>
     </comment>
-    <comment ref="F23" authorId="0" shapeId="0">
+    <comment ref="G36" authorId="0" shapeId="0">
       <text>
         <t>UNVERIFIED: Found via web search; the IG linked to the Spainora Meta ad account is @someho.nl, not Spainora's</t>
       </text>
     </comment>
-    <comment ref="I24" authorId="0" shapeId="0">
+    <comment ref="M37" authorId="0" shapeId="0">
+      <text>
+        <t>UNVERIFIED: Google Maps search link for 'Sushi Sando Claude Debussylaan 33 Amsterdam'. Open it, confirm the listing, and replace it with the listing's share link.</t>
+      </text>
+    </comment>
+    <comment ref="M38" authorId="0" shapeId="0">
+      <text>
+        <t>UNVERIFIED: Google Maps search link for 'Sushi Sando Strandweg 161 Den Haag'. Open it, confirm the listing, and replace it with the listing's share link.</t>
+      </text>
+    </comment>
+    <comment ref="J39" authorId="0" shapeId="0">
       <text>
         <t>UNVERIFIED: Name match only; could belong to tammynailsupply.com, a different company</t>
       </text>
     </comment>
-    <comment ref="L24" authorId="0" shapeId="0">
+    <comment ref="M39" authorId="0" shapeId="0">
       <text>
         <t>UNVERIFIED: Google Maps search link for 'Tammy Nails Supply Spoorsingel 57 Beverwijk'. Open it, confirm the listing, and replace it with the listing's share link.</t>
       </text>
@@ -691,14 +779,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q25"/>
+  <dimension ref="A1:R40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
     <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="34" customWidth="1" min="5" max="5"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
     <col width="34" customWidth="1" min="6" max="6"/>
     <col width="34" customWidth="1" min="7" max="7"/>
     <col width="34" customWidth="1" min="8" max="8"/>
@@ -706,11 +794,12 @@
     <col width="34" customWidth="1" min="10" max="10"/>
     <col width="34" customWidth="1" min="11" max="11"/>
     <col width="34" customWidth="1" min="12" max="12"/>
-    <col width="26" customWidth="1" min="13" max="13"/>
+    <col width="34" customWidth="1" min="13" max="13"/>
     <col width="26" customWidth="1" min="14" max="14"/>
     <col width="26" customWidth="1" min="15" max="15"/>
     <col width="26" customWidth="1" min="16" max="16"/>
-    <col width="70" customWidth="1" min="17" max="17"/>
+    <col width="26" customWidth="1" min="17" max="17"/>
+    <col width="70" customWidth="1" min="18" max="18"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
@@ -726,75 +815,80 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>Branch / Location</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t>Google Ads Status</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Meta Ads Status</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>X Handle</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Instagram</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Facebook</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>LinkedIn</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Pinterest</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>TikTok</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>YouTube</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Google Business</t>
         </is>
       </c>
-      <c r="M1" s="2" t="inlineStr">
+      <c r="N1" s="2" t="inlineStr">
         <is>
           <t>Google Drive Link for Assets</t>
         </is>
       </c>
-      <c r="N1" s="2" t="inlineStr">
+      <c r="O1" s="2" t="inlineStr">
         <is>
           <t>Phone Number</t>
         </is>
       </c>
-      <c r="O1" s="2" t="inlineStr">
+      <c r="P1" s="2" t="inlineStr">
         <is>
           <t>Website</t>
         </is>
       </c>
-      <c r="P1" s="2" t="inlineStr">
+      <c r="Q1" s="2" t="inlineStr">
         <is>
           <t>Address</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
@@ -809,41 +903,46 @@
           <t>ADAMS Wereldkeuken</t>
         </is>
       </c>
-      <c r="C2" s="3" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
-      </c>
-      <c r="D2" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E2" s="6" t="n"/>
-      <c r="F2" s="7" t="inlineStr">
+      <c r="C2" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="E2" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F2" s="6" t="n"/>
+      <c r="G2" s="7" t="inlineStr">
         <is>
           <t>https://www.instagram.com/adamswereldkeuken/</t>
         </is>
       </c>
-      <c r="G2" s="7" t="inlineStr">
+      <c r="H2" s="7" t="inlineStr">
         <is>
           <t>https://www.facebook.com/AdamsWereldkeuken/</t>
         </is>
       </c>
-      <c r="H2" s="6" t="n"/>
       <c r="I2" s="6" t="n"/>
       <c r="J2" s="6" t="n"/>
       <c r="K2" s="6" t="n"/>
-      <c r="L2" s="8" t="inlineStr">
+      <c r="L2" s="6" t="n"/>
+      <c r="M2" s="8" t="inlineStr">
         <is>
           <t>https://www.google.com/maps/search/?api=1&amp;query=ADAMS+Wereldkeuken+Sierenborch+10d+Amsterdam</t>
         </is>
       </c>
-      <c r="M2" s="9" t="n"/>
       <c r="N2" s="9" t="n"/>
       <c r="O2" s="9" t="n"/>
       <c r="P2" s="9" t="n"/>
-      <c r="Q2" s="5" t="inlineStr">
+      <c r="Q2" s="9" t="n"/>
+      <c r="R2" s="5" t="inlineStr">
         <is>
           <t>No own Meta ad account; FB page (ID 266267713770373) is in the business portfolio and promoted via the Spainora ad account. IG from web search (exact handle + Amsterdam).</t>
         </is>
@@ -858,45 +957,50 @@
           <t>Anno Asia</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
-      </c>
-      <c r="D3" s="5" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
-      </c>
-      <c r="E3" s="6" t="n"/>
-      <c r="F3" s="7" t="inlineStr">
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="E3" s="5" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="F3" s="6" t="n"/>
+      <c r="G3" s="7" t="inlineStr">
         <is>
           <t>https://www.instagram.com/annoasia_amsterdam/</t>
         </is>
       </c>
-      <c r="G3" s="7" t="inlineStr">
+      <c r="H3" s="7" t="inlineStr">
         <is>
           <t>https://www.facebook.com/898051420060443</t>
         </is>
       </c>
-      <c r="H3" s="8" t="inlineStr">
+      <c r="I3" s="8" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/in/anno-asia-55428a39a</t>
         </is>
       </c>
-      <c r="I3" s="6" t="n"/>
       <c r="J3" s="6" t="n"/>
       <c r="K3" s="6" t="n"/>
-      <c r="L3" s="8" t="inlineStr">
+      <c r="L3" s="6" t="n"/>
+      <c r="M3" s="8" t="inlineStr">
         <is>
           <t>https://www.google.com/maps/search/?api=1&amp;query=Anno+Asia+Julianaplein+47+Amsterdam</t>
         </is>
       </c>
-      <c r="M3" s="9" t="n"/>
       <c r="N3" s="9" t="n"/>
       <c r="O3" s="9" t="n"/>
       <c r="P3" s="9" t="n"/>
-      <c r="Q3" s="5" t="inlineStr">
+      <c r="Q3" s="9" t="n"/>
+      <c r="R3" s="5" t="inlineStr">
         <is>
           <t>FB + IG confirmed via Meta ad account. No TikTok/YouTube channel found (only third-party videos).</t>
         </is>
@@ -911,45 +1015,50 @@
           <t>Deni Stukadoor</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
-      </c>
-      <c r="D4" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E4" s="6" t="n"/>
-      <c r="F4" s="7" t="inlineStr">
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="E4" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F4" s="6" t="n"/>
+      <c r="G4" s="7" t="inlineStr">
         <is>
           <t>https://www.instagram.com/deni.stukadoor/</t>
         </is>
       </c>
-      <c r="G4" s="8" t="inlineStr">
+      <c r="H4" s="8" t="inlineStr">
         <is>
           <t>https://www.facebook.com/profile.php?id=100081629031709</t>
         </is>
       </c>
-      <c r="H4" s="8" t="inlineStr">
+      <c r="I4" s="8" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/in/deni-stukadoor-5b708a257</t>
         </is>
       </c>
-      <c r="I4" s="6" t="n"/>
       <c r="J4" s="6" t="n"/>
       <c r="K4" s="6" t="n"/>
-      <c r="L4" s="8" t="inlineStr">
+      <c r="L4" s="6" t="n"/>
+      <c r="M4" s="8" t="inlineStr">
         <is>
           <t>https://www.google.com/maps/search/?api=1&amp;query=Deni+Stukadoor+Amsterdam</t>
         </is>
       </c>
-      <c r="M4" s="9" t="n"/>
       <c r="N4" s="9" t="n"/>
       <c r="O4" s="9" t="n"/>
       <c r="P4" s="9" t="n"/>
-      <c r="Q4" s="5" t="inlineStr">
+      <c r="Q4" s="9" t="n"/>
+      <c r="R4" s="5" t="inlineStr">
         <is>
           <t>Google Ads only. Links from web search. Amsterdam-based plasterer.</t>
         </is>
@@ -964,45 +1073,50 @@
           <t>Drukkerij van der Heijden</t>
         </is>
       </c>
-      <c r="C5" s="3" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
-      </c>
-      <c r="D5" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E5" s="6" t="n"/>
-      <c r="F5" s="8" t="inlineStr">
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="E5" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F5" s="6" t="n"/>
+      <c r="G5" s="8" t="inlineStr">
         <is>
           <t>https://www.instagram.com/copyshop_vd_heijden/</t>
         </is>
       </c>
-      <c r="G5" s="7" t="inlineStr">
+      <c r="H5" s="7" t="inlineStr">
         <is>
           <t>https://www.facebook.com/druk.vanderheijden/</t>
         </is>
       </c>
-      <c r="H5" s="7" t="inlineStr">
+      <c r="I5" s="7" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/company/drukkerij-copyshop-vd-heijden</t>
         </is>
       </c>
-      <c r="I5" s="6" t="n"/>
       <c r="J5" s="6" t="n"/>
       <c r="K5" s="6" t="n"/>
-      <c r="L5" s="8" t="inlineStr">
+      <c r="L5" s="6" t="n"/>
+      <c r="M5" s="8" t="inlineStr">
         <is>
           <t>https://www.google.com/maps/search/?api=1&amp;query=Drukkerij+Copyshop+van+der+Heijden+%27s-Hertogenbosch</t>
         </is>
       </c>
-      <c r="M5" s="9" t="n"/>
       <c r="N5" s="9" t="n"/>
       <c r="O5" s="9" t="n"/>
       <c r="P5" s="9" t="n"/>
-      <c r="Q5" s="5" t="inlineStr">
+      <c r="Q5" s="9" t="n"/>
+      <c r="R5" s="5" t="inlineStr">
         <is>
           <t>Google Ads only. Alt IG: instagram.com/drukkerijvanderheijden. Alt LinkedIn: linkedin.com/company/drukkerij-n.-van-der-heijden. Based in 's-Hertogenbosch.</t>
         </is>
@@ -1017,49 +1131,54 @@
           <t>Elmaas</t>
         </is>
       </c>
-      <c r="C6" s="3" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
-      </c>
-      <c r="D6" s="5" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
-      </c>
-      <c r="E6" s="6" t="n"/>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
       <c r="F6" s="6" t="n"/>
-      <c r="G6" s="7" t="inlineStr">
+      <c r="G6" s="6" t="n"/>
+      <c r="H6" s="7" t="inlineStr">
         <is>
           <t>https://www.facebook.com/Elmaas.nl/</t>
         </is>
       </c>
-      <c r="H6" s="7" t="inlineStr">
+      <c r="I6" s="7" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/company/elmaas-technic</t>
         </is>
       </c>
-      <c r="I6" s="6" t="n"/>
-      <c r="J6" s="7" t="inlineStr">
+      <c r="J6" s="6" t="n"/>
+      <c r="K6" s="7" t="inlineStr">
         <is>
           <t>https://www.tiktok.com/@elmaasnl</t>
         </is>
       </c>
-      <c r="K6" s="7" t="inlineStr">
+      <c r="L6" s="7" t="inlineStr">
         <is>
           <t>https://www.youtube.com/@elmaasschuifpuien</t>
         </is>
       </c>
-      <c r="L6" s="8" t="inlineStr">
+      <c r="M6" s="8" t="inlineStr">
         <is>
           <t>https://www.google.com/maps/search/?api=1&amp;query=Elmaas+schuifpuien+Waardenburg</t>
         </is>
       </c>
-      <c r="M6" s="9" t="n"/>
       <c r="N6" s="9" t="n"/>
       <c r="O6" s="9" t="n"/>
       <c r="P6" s="9" t="n"/>
-      <c r="Q6" s="5" t="inlineStr">
+      <c r="Q6" s="9" t="n"/>
+      <c r="R6" s="5" t="inlineStr">
         <is>
           <t>FB confirmed via Meta ad account. No Instagram account is linked to the Meta ad account and none found via search.</t>
         </is>
@@ -1074,37 +1193,42 @@
           <t>Fire Defence</t>
         </is>
       </c>
-      <c r="C7" s="3" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
-      </c>
-      <c r="D7" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E7" s="6" t="n"/>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
       <c r="F7" s="6" t="n"/>
       <c r="G7" s="6" t="n"/>
-      <c r="H7" s="7" t="inlineStr">
+      <c r="H7" s="6" t="n"/>
+      <c r="I7" s="7" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/company/fire-defence-b-v/</t>
         </is>
       </c>
-      <c r="I7" s="6" t="n"/>
       <c r="J7" s="6" t="n"/>
       <c r="K7" s="6" t="n"/>
-      <c r="L7" s="8" t="inlineStr">
+      <c r="L7" s="6" t="n"/>
+      <c r="M7" s="8" t="inlineStr">
         <is>
           <t>https://www.google.com/maps/search/?api=1&amp;query=Fire+Defence+Leonardo+da+Vinciplein+76+Haarlem</t>
         </is>
       </c>
-      <c r="M7" s="9" t="n"/>
       <c r="N7" s="9" t="n"/>
       <c r="O7" s="9" t="n"/>
       <c r="P7" s="9" t="n"/>
-      <c r="Q7" s="5" t="inlineStr">
+      <c r="Q7" s="9" t="n"/>
+      <c r="R7" s="5" t="inlineStr">
         <is>
           <t>Google Ads only. Trades as 'Firedefence services &amp; systems' (firedefence.eu). No FB/IG/TikTok/YouTube found.</t>
         </is>
@@ -1119,49 +1243,54 @@
           <t>Foodhall Scheveningen</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
-      </c>
-      <c r="D8" s="5" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
-      </c>
-      <c r="E8" s="6" t="n"/>
-      <c r="F8" s="7" t="inlineStr">
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="F8" s="6" t="n"/>
+      <c r="G8" s="7" t="inlineStr">
         <is>
           <t>https://www.instagram.com/foodhall.scheveningen/</t>
         </is>
       </c>
-      <c r="G8" s="7" t="inlineStr">
+      <c r="H8" s="7" t="inlineStr">
         <is>
           <t>https://www.facebook.com/107058017455273</t>
         </is>
       </c>
-      <c r="H8" s="6" t="n"/>
       <c r="I8" s="6" t="n"/>
-      <c r="J8" s="7" t="inlineStr">
+      <c r="J8" s="6" t="n"/>
+      <c r="K8" s="7" t="inlineStr">
         <is>
           <t>https://www.tiktok.com/@foodhallscheveningen</t>
         </is>
       </c>
-      <c r="K8" s="8" t="inlineStr">
+      <c r="L8" s="8" t="inlineStr">
         <is>
           <t>https://www.youtube.com/@foodhallscheveningen5894</t>
         </is>
       </c>
-      <c r="L8" s="8" t="inlineStr">
+      <c r="M8" s="8" t="inlineStr">
         <is>
           <t>https://www.google.com/maps/search/?api=1&amp;query=Foodhall+Scheveningen</t>
         </is>
       </c>
-      <c r="M8" s="9" t="n"/>
       <c r="N8" s="9" t="n"/>
       <c r="O8" s="9" t="n"/>
       <c r="P8" s="9" t="n"/>
-      <c r="Q8" s="5" t="inlineStr">
+      <c r="Q8" s="9" t="n"/>
+      <c r="R8" s="5" t="inlineStr">
         <is>
           <t>Meta account is named 'Foodhallen Scheveningen'. FB + IG confirmed via Meta.</t>
         </is>
@@ -1176,49 +1305,54 @@
           <t>Genki Garden (Restaurant GENKI)</t>
         </is>
       </c>
-      <c r="C9" s="3" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
-      </c>
-      <c r="D9" s="10" t="inlineStr">
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="E9" s="10" t="inlineStr">
         <is>
           <t>Unsettled</t>
         </is>
       </c>
-      <c r="E9" s="8" t="inlineStr">
+      <c r="F9" s="8" t="inlineStr">
         <is>
           <t>https://x.com/genkigarden</t>
         </is>
       </c>
-      <c r="F9" s="7" t="inlineStr">
+      <c r="G9" s="7" t="inlineStr">
         <is>
           <t>https://www.instagram.com/restaurantgenki/</t>
         </is>
       </c>
-      <c r="G9" s="7" t="inlineStr">
+      <c r="H9" s="7" t="inlineStr">
         <is>
           <t>https://www.facebook.com/122834841096176</t>
         </is>
       </c>
-      <c r="H9" s="6" t="n"/>
       <c r="I9" s="6" t="n"/>
-      <c r="J9" s="7" t="inlineStr">
+      <c r="J9" s="6" t="n"/>
+      <c r="K9" s="7" t="inlineStr">
         <is>
           <t>https://www.tiktok.com/@restaurantgenki</t>
         </is>
       </c>
-      <c r="K9" s="6" t="n"/>
-      <c r="L9" s="8" t="inlineStr">
+      <c r="L9" s="6" t="n"/>
+      <c r="M9" s="8" t="inlineStr">
         <is>
           <t>https://www.google.com/maps/search/?api=1&amp;query=Genki+Garden+Reguliersdwarsstraat+26+Amsterdam</t>
         </is>
       </c>
-      <c r="M9" s="9" t="n"/>
       <c r="N9" s="9" t="n"/>
       <c r="O9" s="9" t="n"/>
       <c r="P9" s="9" t="n"/>
-      <c r="Q9" s="5" t="inlineStr">
+      <c r="Q9" s="9" t="n"/>
+      <c r="R9" s="5" t="inlineStr">
         <is>
           <t>Meta ad account status = UNSETTLED (payment issue). FB + IG confirmed via Meta. Alt X: x.com/restaurantgenki.</t>
         </is>
@@ -1233,45 +1367,50 @@
           <t>Glasservice Noord</t>
         </is>
       </c>
-      <c r="C10" s="3" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
-      </c>
-      <c r="D10" s="5" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
-      </c>
-      <c r="E10" s="6" t="n"/>
-      <c r="F10" s="7" t="inlineStr">
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="F10" s="6" t="n"/>
+      <c r="G10" s="7" t="inlineStr">
         <is>
           <t>https://www.instagram.com/glasservicenoord.vanopdorpglas/</t>
         </is>
       </c>
-      <c r="G10" s="7" t="inlineStr">
+      <c r="H10" s="7" t="inlineStr">
         <is>
           <t>https://www.facebook.com/glasservicenoord/</t>
         </is>
       </c>
-      <c r="H10" s="6" t="n"/>
       <c r="I10" s="6" t="n"/>
       <c r="J10" s="6" t="n"/>
-      <c r="K10" s="7" t="inlineStr">
+      <c r="K10" s="6" t="n"/>
+      <c r="L10" s="7" t="inlineStr">
         <is>
           <t>https://www.youtube.com/@GlasserviceNoord</t>
         </is>
       </c>
-      <c r="L10" s="8" t="inlineStr">
+      <c r="M10" s="8" t="inlineStr">
         <is>
           <t>https://www.google.com/maps/search/?api=1&amp;query=Glasservice+Noord+Spanjaardwaard+43+%27s-Hertogenbosch</t>
         </is>
       </c>
-      <c r="M10" s="9" t="n"/>
       <c r="N10" s="9" t="n"/>
       <c r="O10" s="9" t="n"/>
       <c r="P10" s="9" t="n"/>
-      <c r="Q10" s="5" t="inlineStr">
+      <c r="Q10" s="9" t="n"/>
+      <c r="R10" s="5" t="inlineStr">
         <is>
           <t>Brand on Meta: 'Glasservice Noord &amp; van Opdorp Glas'. FB + IG confirmed via Meta.</t>
         </is>
@@ -1286,49 +1425,54 @@
           <t>Hotspot Fishing</t>
         </is>
       </c>
-      <c r="C11" s="3" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
-      </c>
-      <c r="D11" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E11" s="8" t="inlineStr">
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="E11" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F11" s="8" t="inlineStr">
         <is>
           <t>https://x.com/hotspotfishing</t>
         </is>
       </c>
-      <c r="F11" s="7" t="inlineStr">
+      <c r="G11" s="7" t="inlineStr">
         <is>
           <t>https://www.instagram.com/hotspotfishing.nl/</t>
         </is>
       </c>
-      <c r="G11" s="7" t="inlineStr">
+      <c r="H11" s="7" t="inlineStr">
         <is>
           <t>https://www.facebook.com/p/Hotspot-Fishing-100063604866752/</t>
         </is>
       </c>
-      <c r="H11" s="6" t="n"/>
       <c r="I11" s="6" t="n"/>
       <c r="J11" s="6" t="n"/>
-      <c r="K11" s="8" t="inlineStr">
+      <c r="K11" s="6" t="n"/>
+      <c r="L11" s="8" t="inlineStr">
         <is>
           <t>https://www.youtube.com/@hotspotfishing9088</t>
         </is>
       </c>
-      <c r="L11" s="8" t="inlineStr">
+      <c r="M11" s="8" t="inlineStr">
         <is>
           <t>https://www.google.com/maps/search/?api=1&amp;query=Hotspot+Fishing+Rijpwetering</t>
         </is>
       </c>
-      <c r="M11" s="9" t="n"/>
       <c r="N11" s="9" t="n"/>
       <c r="O11" s="9" t="n"/>
       <c r="P11" s="9" t="n"/>
-      <c r="Q11" s="5" t="inlineStr">
+      <c r="Q11" s="9" t="n"/>
+      <c r="R11" s="5" t="inlineStr">
         <is>
           <t>Google Ads only. Predator-fishing shop in Rijpwetering.</t>
         </is>
@@ -1343,45 +1487,50 @@
           <t>Just Dai</t>
         </is>
       </c>
-      <c r="C12" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D12" s="10" t="inlineStr">
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E12" s="10" t="inlineStr">
         <is>
           <t>Pending closure / Active</t>
         </is>
       </c>
-      <c r="E12" s="6" t="n"/>
-      <c r="F12" s="7" t="inlineStr">
+      <c r="F12" s="6" t="n"/>
+      <c r="G12" s="7" t="inlineStr">
         <is>
           <t>https://www.instagram.com/justdai_fashion/</t>
         </is>
       </c>
-      <c r="G12" s="7" t="inlineStr">
+      <c r="H12" s="7" t="inlineStr">
         <is>
           <t>https://www.facebook.com/justdai.nl/</t>
         </is>
       </c>
-      <c r="H12" s="6" t="n"/>
       <c r="I12" s="6" t="n"/>
-      <c r="J12" s="7" t="inlineStr">
+      <c r="J12" s="6" t="n"/>
+      <c r="K12" s="7" t="inlineStr">
         <is>
           <t>https://www.tiktok.com/@justdai.nl</t>
         </is>
       </c>
-      <c r="K12" s="6" t="n"/>
-      <c r="L12" s="8" t="inlineStr">
+      <c r="L12" s="6" t="n"/>
+      <c r="M12" s="8" t="inlineStr">
         <is>
           <t>https://www.google.com/maps/search/?api=1&amp;query=Just+Dai+Koningin+Wilhelminaplein+13+Amsterdam</t>
         </is>
       </c>
-      <c r="M12" s="9" t="n"/>
       <c r="N12" s="9" t="n"/>
       <c r="O12" s="9" t="n"/>
       <c r="P12" s="9" t="n"/>
-      <c r="Q12" s="5" t="inlineStr">
+      <c r="Q12" s="9" t="n"/>
+      <c r="R12" s="5" t="inlineStr">
         <is>
           <t>Meta only: 'Just Dai' (pending closure) + 'Just Dai 2026' (active). The Meta connector has no access to either account's pages, so links come from web search. Fashion wholesale/webshop, World Fashion Centre Amsterdam.</t>
         </is>
@@ -1393,50 +1542,51 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>Landgoed Groenendaal</t>
-        </is>
-      </c>
-      <c r="C13" s="3" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
-      </c>
-      <c r="D13" s="5" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
-      </c>
-      <c r="E13" s="6" t="n"/>
-      <c r="F13" s="7" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/landgoed_groenendaal/</t>
-        </is>
-      </c>
+          <t>L'albero</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>Amsterdam</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E13" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F13" s="6" t="n"/>
       <c r="G13" s="7" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/496849033673500</t>
-        </is>
-      </c>
-      <c r="H13" s="7" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/company/landgoed-groenendaal</t>
-        </is>
-      </c>
+          <t>https://www.instagram.com/lalberoamsterdam/</t>
+        </is>
+      </c>
+      <c r="H13" s="6" t="n"/>
       <c r="I13" s="6" t="n"/>
       <c r="J13" s="6" t="n"/>
       <c r="K13" s="6" t="n"/>
-      <c r="L13" s="8" t="inlineStr">
-        <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=Landgoed+Groenendaal+Groenendaal+3+Heemstede</t>
-        </is>
-      </c>
-      <c r="M13" s="9" t="n"/>
+      <c r="L13" s="6" t="n"/>
+      <c r="M13" s="8" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=L%27albero+Leidsekruisstraat+30+Amsterdam</t>
+        </is>
+      </c>
       <c r="N13" s="9" t="n"/>
       <c r="O13" s="9" t="n"/>
-      <c r="P13" s="9" t="n"/>
-      <c r="Q13" s="5" t="inlineStr">
-        <is>
-          <t>Meta ad account is not yet enabled for the Meta MCP; FB page found in the business portfolio. IG from web search.</t>
+      <c r="P13" s="11" t="inlineStr">
+        <is>
+          <t>https://lalbero.nl/</t>
+        </is>
+      </c>
+      <c r="Q13" s="9" t="n"/>
+      <c r="R13" s="5" t="inlineStr">
+        <is>
+          <t>Italian restaurant, Leidsekruisstraat 30, 1017 RJ Amsterdam. No Facebook/TikTok found. Same street address as Peppino (Leidsekruisstraat 30-32), so possibly the same owner. Not found as its own ad account (added on request).</t>
         </is>
       </c>
     </row>
@@ -1446,46 +1596,55 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>Madam Chen</t>
-        </is>
-      </c>
-      <c r="C14" s="3" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
-      </c>
-      <c r="D14" s="5" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
-      </c>
-      <c r="E14" s="6" t="n"/>
-      <c r="F14" s="7" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/madamchen_rotterdam/</t>
-        </is>
-      </c>
+          <t>Landgoed Groenendaal</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="E14" s="5" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="F14" s="6" t="n"/>
       <c r="G14" s="7" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/308034966403840</t>
-        </is>
-      </c>
-      <c r="H14" s="6" t="n"/>
-      <c r="I14" s="6" t="n"/>
+          <t>https://www.instagram.com/landgoed_groenendaal/</t>
+        </is>
+      </c>
+      <c r="H14" s="7" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/496849033673500</t>
+        </is>
+      </c>
+      <c r="I14" s="7" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/landgoed-groenendaal</t>
+        </is>
+      </c>
       <c r="J14" s="6" t="n"/>
       <c r="K14" s="6" t="n"/>
-      <c r="L14" s="8" t="inlineStr">
-        <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=Madam+Chen+Kolk+50B+Rotterdam</t>
-        </is>
-      </c>
-      <c r="M14" s="9" t="n"/>
+      <c r="L14" s="6" t="n"/>
+      <c r="M14" s="8" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=Landgoed+Groenendaal+Groenendaal+3+Heemstede</t>
+        </is>
+      </c>
       <c r="N14" s="9" t="n"/>
       <c r="O14" s="9" t="n"/>
       <c r="P14" s="9" t="n"/>
-      <c r="Q14" s="5" t="inlineStr">
-        <is>
-          <t>FB + IG confirmed via Meta. No official TikTok found (only discover/third-party videos).</t>
+      <c r="Q14" s="9" t="n"/>
+      <c r="R14" s="5" t="inlineStr">
+        <is>
+          <t>Meta ad account is not yet enabled for the Meta MCP; FB page found in the business portfolio. IG from web search.</t>
         </is>
       </c>
     </row>
@@ -1495,54 +1654,51 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>Oran Aesthetics</t>
-        </is>
-      </c>
-      <c r="C15" s="3" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
-      </c>
-      <c r="D15" s="5" t="inlineStr">
-        <is>
-          <t>Active (2 accounts)</t>
-        </is>
-      </c>
-      <c r="E15" s="6" t="n"/>
-      <c r="F15" s="7" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/oran_aesthetics/</t>
-        </is>
-      </c>
+          <t>Madam Chen</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="E15" s="5" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="F15" s="6" t="n"/>
       <c r="G15" s="7" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/fillersbyoran/</t>
-        </is>
-      </c>
-      <c r="H15" s="6" t="n"/>
+          <t>https://www.instagram.com/madamchen_rotterdam/</t>
+        </is>
+      </c>
+      <c r="H15" s="7" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/308034966403840</t>
+        </is>
+      </c>
       <c r="I15" s="6" t="n"/>
-      <c r="J15" s="7" t="inlineStr">
-        <is>
-          <t>https://www.tiktok.com/@oran_aesthetics</t>
-        </is>
-      </c>
-      <c r="K15" s="7" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/@oranaesthetics</t>
-        </is>
-      </c>
-      <c r="L15" s="8" t="inlineStr">
-        <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=Oran+Aesthetics+Arent+Janszoon+Ernststraat+Amsterdam</t>
-        </is>
-      </c>
-      <c r="M15" s="9" t="n"/>
+      <c r="J15" s="6" t="n"/>
+      <c r="K15" s="6" t="n"/>
+      <c r="L15" s="6" t="n"/>
+      <c r="M15" s="8" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=Madam+Chen+Kolk+50B+Rotterdam</t>
+        </is>
+      </c>
       <c r="N15" s="9" t="n"/>
       <c r="O15" s="9" t="n"/>
       <c r="P15" s="9" t="n"/>
-      <c r="Q15" s="5" t="inlineStr">
-        <is>
-          <t>Google account is named 'Oran'. Meta: 'Oran Aesthetics Ad' + 'Oran Aesthetics Ads 2023' (connector has no access to the first). FB + IG confirmed via Meta.</t>
+      <c r="Q15" s="9" t="n"/>
+      <c r="R15" s="5" t="inlineStr">
+        <is>
+          <t>FB + IG confirmed via Meta. No official TikTok found (only discover/third-party videos).</t>
         </is>
       </c>
     </row>
@@ -1552,46 +1708,59 @@
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>Oriental Noordwijkerhout</t>
-        </is>
-      </c>
-      <c r="C16" s="3" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
-      </c>
-      <c r="D16" s="10" t="inlineStr">
-        <is>
-          <t>Unsettled</t>
-        </is>
-      </c>
-      <c r="E16" s="6" t="n"/>
-      <c r="F16" s="7" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/oriental_nwh/</t>
-        </is>
-      </c>
+          <t>Oran Aesthetics</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="E16" s="5" t="inlineStr">
+        <is>
+          <t>Active (2 accounts)</t>
+        </is>
+      </c>
+      <c r="F16" s="6" t="n"/>
       <c r="G16" s="7" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/215610705143215</t>
-        </is>
-      </c>
-      <c r="H16" s="6" t="n"/>
+          <t>https://www.instagram.com/oran_aesthetics/</t>
+        </is>
+      </c>
+      <c r="H16" s="7" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/fillersbyoran/</t>
+        </is>
+      </c>
       <c r="I16" s="6" t="n"/>
       <c r="J16" s="6" t="n"/>
-      <c r="K16" s="6" t="n"/>
-      <c r="L16" s="8" t="inlineStr">
-        <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=Wokrestaurant+Oriental+Langelaan+2a+Noordwijkerhout</t>
-        </is>
-      </c>
-      <c r="M16" s="9" t="n"/>
+      <c r="K16" s="7" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@oran_aesthetics</t>
+        </is>
+      </c>
+      <c r="L16" s="7" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/@oranaesthetics</t>
+        </is>
+      </c>
+      <c r="M16" s="8" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=Oran+Aesthetics+Arent+Janszoon+Ernststraat+Amsterdam</t>
+        </is>
+      </c>
       <c r="N16" s="9" t="n"/>
       <c r="O16" s="9" t="n"/>
       <c r="P16" s="9" t="n"/>
-      <c r="Q16" s="5" t="inlineStr">
-        <is>
-          <t>Meta ad account status = UNSETTLED. FB page 'Wokrestaurant Oriental in de Flamingo Partycenter' confirmed via Meta. IG from web search.</t>
+      <c r="Q16" s="9" t="n"/>
+      <c r="R16" s="5" t="inlineStr">
+        <is>
+          <t>Google account is named 'Oran'. Meta: 'Oran Aesthetics Ad' + 'Oran Aesthetics Ads 2023' (connector has no access to the first). FB + IG confirmed via Meta.</t>
         </is>
       </c>
     </row>
@@ -1601,50 +1770,51 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>Restaurant ChouChou</t>
-        </is>
-      </c>
-      <c r="C17" s="3" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
-      </c>
-      <c r="D17" s="5" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
-      </c>
-      <c r="E17" s="6" t="n"/>
-      <c r="F17" s="7" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/chouchou_scheveningen/</t>
-        </is>
-      </c>
+          <t>Oriental Noordwijkerhout</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="E17" s="10" t="inlineStr">
+        <is>
+          <t>Unsettled</t>
+        </is>
+      </c>
+      <c r="F17" s="6" t="n"/>
       <c r="G17" s="7" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/restaurantchouchou/</t>
-        </is>
-      </c>
-      <c r="H17" s="6" t="n"/>
+          <t>https://www.instagram.com/oriental_nwh/</t>
+        </is>
+      </c>
+      <c r="H17" s="7" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/215610705143215</t>
+        </is>
+      </c>
       <c r="I17" s="6" t="n"/>
-      <c r="J17" s="7" t="inlineStr">
-        <is>
-          <t>https://www.tiktok.com/@chouchou_scheveningen</t>
-        </is>
-      </c>
+      <c r="J17" s="6" t="n"/>
       <c r="K17" s="6" t="n"/>
-      <c r="L17" s="8" t="inlineStr">
-        <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=Restaurant+ChouChou+Strandweg+159+Den+Haag</t>
-        </is>
-      </c>
-      <c r="M17" s="9" t="n"/>
+      <c r="L17" s="6" t="n"/>
+      <c r="M17" s="8" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=Wokrestaurant+Oriental+Langelaan+2a+Noordwijkerhout</t>
+        </is>
+      </c>
       <c r="N17" s="9" t="n"/>
       <c r="O17" s="9" t="n"/>
       <c r="P17" s="9" t="n"/>
-      <c r="Q17" s="5" t="inlineStr">
-        <is>
-          <t>Meta account named 'ChouChou Someho'. FB + IG confirmed via Meta.</t>
+      <c r="Q17" s="9" t="n"/>
+      <c r="R17" s="5" t="inlineStr">
+        <is>
+          <t>Meta ad account status = UNSETTLED. FB page 'Wokrestaurant Oriental in de Flamingo Partycenter' confirmed via Meta. IG from web search.</t>
         </is>
       </c>
     </row>
@@ -1654,50 +1824,39 @@
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>Restaurant De Gouden Wok Zuiderpark</t>
-        </is>
-      </c>
-      <c r="C18" s="3" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
-      </c>
-      <c r="D18" s="5" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
-      </c>
-      <c r="E18" s="6" t="n"/>
-      <c r="F18" s="7" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/degoudenwokzuiderpark/</t>
-        </is>
-      </c>
-      <c r="G18" s="7" t="inlineStr">
-        <is>
-          <t>https://www.facebook.com/GoudenWok/</t>
-        </is>
-      </c>
+          <t>Outstanding Quotes</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>Netherlands</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E18" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F18" s="6" t="n"/>
+      <c r="G18" s="6" t="n"/>
       <c r="H18" s="6" t="n"/>
       <c r="I18" s="6" t="n"/>
-      <c r="J18" s="7" t="inlineStr">
-        <is>
-          <t>https://www.tiktok.com/@degoudenwok</t>
-        </is>
-      </c>
+      <c r="J18" s="6" t="n"/>
       <c r="K18" s="6" t="n"/>
-      <c r="L18" s="8" t="inlineStr">
-        <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=De+Gouden+Wok+Zuiderpark+Den+Haag</t>
-        </is>
-      </c>
-      <c r="M18" s="9" t="n"/>
+      <c r="L18" s="6" t="n"/>
+      <c r="M18" s="6" t="n"/>
       <c r="N18" s="9" t="n"/>
       <c r="O18" s="9" t="n"/>
       <c r="P18" s="9" t="n"/>
-      <c r="Q18" s="5" t="inlineStr">
-        <is>
-          <t>FB + IG confirmed via Meta. The same Meta ad account also promotes 'Khlay Zen Thais Massagesalon Rotterdam', which may be a separate client.</t>
+      <c r="Q18" s="9" t="n"/>
+      <c r="R18" s="5" t="inlineStr">
+        <is>
+          <t>No matching Dutch business or social profiles found online. Please share their website or what they do and I'll re-check.</t>
         </is>
       </c>
     </row>
@@ -1707,46 +1866,59 @@
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>Restaurant Guru</t>
-        </is>
-      </c>
-      <c r="C19" s="3" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
-      </c>
-      <c r="D19" s="5" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
-      </c>
-      <c r="E19" s="6" t="n"/>
-      <c r="F19" s="7" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/guru_amsterdam/</t>
-        </is>
-      </c>
+          <t>Pad Thai (Pad Thai World)</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>Amsterdam – Berenstraat</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E19" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F19" s="6" t="n"/>
       <c r="G19" s="7" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/Guruamsterdam/</t>
-        </is>
-      </c>
-      <c r="H19" s="6" t="n"/>
-      <c r="I19" s="6" t="n"/>
+          <t>https://www.instagram.com/padthaiworld/</t>
+        </is>
+      </c>
+      <c r="H19" s="7" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/padthaiberenstraat/</t>
+        </is>
+      </c>
+      <c r="I19" s="7" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/pad-thai-world</t>
+        </is>
+      </c>
       <c r="J19" s="6" t="n"/>
       <c r="K19" s="6" t="n"/>
-      <c r="L19" s="8" t="inlineStr">
-        <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=Guru+Restaurant+Rijnstraat+157+Amsterdam</t>
-        </is>
-      </c>
-      <c r="M19" s="9" t="n"/>
+      <c r="L19" s="6" t="n"/>
+      <c r="M19" s="8" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=Pad+Thai+Berenstraat+20H+Amsterdam</t>
+        </is>
+      </c>
       <c r="N19" s="9" t="n"/>
       <c r="O19" s="9" t="n"/>
-      <c r="P19" s="9" t="n"/>
-      <c r="Q19" s="5" t="inlineStr">
-        <is>
-          <t>Meta account named 'Guru Indian restaurant'. FB + IG confirmed via Meta.</t>
+      <c r="P19" s="11" t="inlineStr">
+        <is>
+          <t>https://padthai.nl/</t>
+        </is>
+      </c>
+      <c r="Q19" s="9" t="n"/>
+      <c r="R19" s="5" t="inlineStr">
+        <is>
+          <t>Address: Berenstraat 20H, 1016 GH Amsterdam (Nine Streets). Instagram, LinkedIn and website are shared by all branches. Not found as its own Google/Meta ad account (added on request).</t>
         </is>
       </c>
     </row>
@@ -1756,50 +1928,59 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>Restaurant Lavash</t>
-        </is>
-      </c>
-      <c r="C20" s="3" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
-      </c>
-      <c r="D20" s="5" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
-      </c>
-      <c r="E20" s="6" t="n"/>
-      <c r="F20" s="7" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/atlavash/</t>
-        </is>
-      </c>
+          <t>Pad Thai (Pad Thai World)</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>Amsterdam – Kinkerstraat</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E20" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F20" s="6" t="n"/>
       <c r="G20" s="7" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/LavashNL/</t>
+          <t>https://www.instagram.com/padthaiworld/</t>
         </is>
       </c>
       <c r="H20" s="7" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/restaurant-lavash</t>
-        </is>
-      </c>
-      <c r="I20" s="6" t="n"/>
+          <t>https://www.facebook.com/padthaikinkerstraat/</t>
+        </is>
+      </c>
+      <c r="I20" s="7" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/pad-thai-world</t>
+        </is>
+      </c>
       <c r="J20" s="6" t="n"/>
       <c r="K20" s="6" t="n"/>
-      <c r="L20" s="8" t="inlineStr">
-        <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=Restaurant+Lavash+Korte+Leidsedwarsstraat+119+Amsterdam</t>
-        </is>
-      </c>
-      <c r="M20" s="9" t="n"/>
+      <c r="L20" s="6" t="n"/>
+      <c r="M20" s="8" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=Pad+Thai+Kinkerstraat+142+Amsterdam</t>
+        </is>
+      </c>
       <c r="N20" s="9" t="n"/>
       <c r="O20" s="9" t="n"/>
-      <c r="P20" s="9" t="n"/>
-      <c r="Q20" s="5" t="inlineStr">
-        <is>
-          <t>FB + IG confirmed via Meta. The same Meta ad account also holds 'Peppino Amsterdam' (FB + IG @peppinoamsterdamnl).</t>
+      <c r="P20" s="11" t="inlineStr">
+        <is>
+          <t>https://padthai.nl/</t>
+        </is>
+      </c>
+      <c r="Q20" s="9" t="n"/>
+      <c r="R20" s="5" t="inlineStr">
+        <is>
+          <t>Address: Kinkerstraat 142, Amsterdam. Instagram, LinkedIn and website are shared by all branches. Not found as its own Google/Meta ad account (added on request).</t>
         </is>
       </c>
     </row>
@@ -1809,50 +1990,59 @@
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>SKT (SK Tekenwerk)</t>
-        </is>
-      </c>
-      <c r="C21" s="3" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
-      </c>
-      <c r="D21" s="5" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
-      </c>
-      <c r="E21" s="6" t="n"/>
-      <c r="F21" s="8" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/sktekenwerk/</t>
-        </is>
-      </c>
+          <t>Pad Thai (Pad Thai World)</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>Amsterdam – Zeedijk</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E21" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F21" s="6" t="n"/>
       <c r="G21" s="7" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/1061694200366933</t>
+          <t>https://www.instagram.com/padthaiworld/</t>
         </is>
       </c>
       <c r="H21" s="7" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/snel-kwaliteit-tekenwerk</t>
-        </is>
-      </c>
-      <c r="I21" s="6" t="n"/>
+          <t>https://www.facebook.com/padthaizeedijk/</t>
+        </is>
+      </c>
+      <c r="I21" s="7" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/pad-thai-world</t>
+        </is>
+      </c>
       <c r="J21" s="6" t="n"/>
       <c r="K21" s="6" t="n"/>
-      <c r="L21" s="8" t="inlineStr">
-        <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=SK+Tekenwerk</t>
-        </is>
-      </c>
-      <c r="M21" s="9" t="n"/>
+      <c r="L21" s="6" t="n"/>
+      <c r="M21" s="8" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=Pad+Thai+Zeedijk+119+Amsterdam</t>
+        </is>
+      </c>
       <c r="N21" s="9" t="n"/>
       <c r="O21" s="9" t="n"/>
-      <c r="P21" s="9" t="n"/>
-      <c r="Q21" s="5" t="inlineStr">
-        <is>
-          <t>SKT = 'Snel Kwaliteit Tekenwerk' (sktekenwerk.nl). Meta ad account not yet enabled for the Meta MCP; FB page 'SK Tekenwerk' found in the business portfolio.</t>
+      <c r="P21" s="11" t="inlineStr">
+        <is>
+          <t>https://padthai.nl/</t>
+        </is>
+      </c>
+      <c r="Q21" s="9" t="n"/>
+      <c r="R21" s="5" t="inlineStr">
+        <is>
+          <t>Address: Zeedijk 119, 1012 AW Amsterdam. Instagram, LinkedIn and website are shared by all branches. Not found as its own Google/Meta ad account (added on request).</t>
         </is>
       </c>
     </row>
@@ -1862,46 +2052,59 @@
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>SOMEHO</t>
-        </is>
-      </c>
-      <c r="C22" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D22" s="5" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
-      </c>
-      <c r="E22" s="6" t="n"/>
-      <c r="F22" s="7" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/someho.nl/</t>
-        </is>
-      </c>
+          <t>Pad Thai (Pad Thai World)</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>Den Haag – Noordeinde</t>
+        </is>
+      </c>
+      <c r="D22" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E22" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F22" s="6" t="n"/>
       <c r="G22" s="7" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/101093459711793</t>
-        </is>
-      </c>
-      <c r="H22" s="6" t="n"/>
-      <c r="I22" s="6" t="n"/>
+          <t>https://www.instagram.com/padthaiworld/</t>
+        </is>
+      </c>
+      <c r="H22" s="7" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/padthainoordeinde/</t>
+        </is>
+      </c>
+      <c r="I22" s="7" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/pad-thai-world</t>
+        </is>
+      </c>
       <c r="J22" s="6" t="n"/>
       <c r="K22" s="6" t="n"/>
-      <c r="L22" s="8" t="inlineStr">
-        <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=SOMEHO+Cruquiuszoom+55+Cruquius</t>
-        </is>
-      </c>
-      <c r="M22" s="9" t="n"/>
+      <c r="L22" s="6" t="n"/>
+      <c r="M22" s="8" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=Pad+Thai+Noordeinde+13+Den+Haag</t>
+        </is>
+      </c>
       <c r="N22" s="9" t="n"/>
       <c r="O22" s="9" t="n"/>
-      <c r="P22" s="9" t="n"/>
-      <c r="Q22" s="5" t="inlineStr">
-        <is>
-          <t>Meta only. Hospitality marketing agency (part of M&amp;A Marketing). Kept as its own client row as requested.</t>
+      <c r="P22" s="11" t="inlineStr">
+        <is>
+          <t>https://padthai.nl/</t>
+        </is>
+      </c>
+      <c r="Q22" s="9" t="n"/>
+      <c r="R22" s="5" t="inlineStr">
+        <is>
+          <t>Address: Noordeinde 13, Den Haag. Instagram, LinkedIn and website are shared by all branches. Not found as its own Google/Meta ad account (added on request).</t>
         </is>
       </c>
     </row>
@@ -1911,54 +2114,55 @@
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>Spainora</t>
-        </is>
-      </c>
-      <c r="C23" s="3" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
-      </c>
-      <c r="D23" s="5" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
-      </c>
-      <c r="E23" s="7" t="inlineStr">
-        <is>
-          <t>https://x.com/spainora_com</t>
-        </is>
-      </c>
-      <c r="F23" s="8" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/spainora.official/</t>
-        </is>
-      </c>
+          <t>Pad Thai (Pad Thai World)</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>Leidschendam – Westfield Mall</t>
+        </is>
+      </c>
+      <c r="D23" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E23" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F23" s="6" t="n"/>
       <c r="G23" s="7" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/spainora/</t>
+          <t>https://www.instagram.com/padthaiworld/</t>
         </is>
       </c>
       <c r="H23" s="6" t="n"/>
-      <c r="I23" s="6" t="n"/>
-      <c r="J23" s="7" t="inlineStr">
-        <is>
-          <t>https://www.tiktok.com/@spainora</t>
-        </is>
-      </c>
-      <c r="K23" s="7" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/@spainora</t>
-        </is>
-      </c>
+      <c r="I23" s="7" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/pad-thai-world</t>
+        </is>
+      </c>
+      <c r="J23" s="6" t="n"/>
+      <c r="K23" s="6" t="n"/>
       <c r="L23" s="6" t="n"/>
-      <c r="M23" s="9" t="n"/>
+      <c r="M23" s="8" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=Pad+Thai+Westfield+Mall+Kornoelje+119+Leidschendam</t>
+        </is>
+      </c>
       <c r="N23" s="9" t="n"/>
       <c r="O23" s="9" t="n"/>
-      <c r="P23" s="9" t="n"/>
-      <c r="Q23" s="5" t="inlineStr">
-        <is>
-          <t>Online real-estate guide (Arevium Capital B.V.), no physical location, so Google Business is left blank. FB page confirmed via Meta.</t>
+      <c r="P23" s="11" t="inlineStr">
+        <is>
+          <t>https://padthai.nl/</t>
+        </is>
+      </c>
+      <c r="Q23" s="9" t="n"/>
+      <c r="R23" s="5" t="inlineStr">
+        <is>
+          <t>Address: Kornoelje 119, 2262 AX Leidschendam. No branch Facebook page found. Instagram, LinkedIn and website are shared by all branches. Not found as its own Google/Meta ad account (added on request).</t>
         </is>
       </c>
     </row>
@@ -1968,50 +2172,55 @@
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>Tammy Nails Supply</t>
-        </is>
-      </c>
-      <c r="C24" s="3" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
-      </c>
-      <c r="D24" s="5" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
-      </c>
-      <c r="E24" s="6" t="n"/>
-      <c r="F24" s="7" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/tammynailsupply_official/</t>
-        </is>
-      </c>
+          <t>Pad Thai (Pad Thai World)</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>Utrecht</t>
+        </is>
+      </c>
+      <c r="D24" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E24" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F24" s="6" t="n"/>
       <c r="G24" s="7" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/tammy.supplynail/</t>
+          <t>https://www.instagram.com/padthaiworld/</t>
         </is>
       </c>
       <c r="H24" s="6" t="n"/>
-      <c r="I24" s="8" t="inlineStr">
-        <is>
-          <t>https://www.pinterest.com/tammynailsupply/</t>
+      <c r="I24" s="7" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/pad-thai-world</t>
         </is>
       </c>
       <c r="J24" s="6" t="n"/>
       <c r="K24" s="6" t="n"/>
-      <c r="L24" s="8" t="inlineStr">
-        <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=Tammy+Nails+Supply+Spoorsingel+57+Beverwijk</t>
-        </is>
-      </c>
-      <c r="M24" s="9" t="n"/>
+      <c r="L24" s="6" t="n"/>
+      <c r="M24" s="8" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=Pad+Thai+World+Utrecht</t>
+        </is>
+      </c>
       <c r="N24" s="9" t="n"/>
       <c r="O24" s="9" t="n"/>
-      <c r="P24" s="9" t="n"/>
-      <c r="Q24" s="5" t="inlineStr">
-        <is>
-          <t>Meta account named 'Tammy Nails Supply'; FB page 'Tammy Nail Supply'. FB + IG confirmed via Meta. Webshop tammynailsupply.nl.</t>
+      <c r="P24" s="11" t="inlineStr">
+        <is>
+          <t>https://padthai.nl/</t>
+        </is>
+      </c>
+      <c r="Q24" s="9" t="n"/>
+      <c r="R24" s="5" t="inlineStr">
+        <is>
+          <t>UNCONFIRMED BRANCH: opening announced, address not found. Instagram, LinkedIn and website are shared by all branches. Not found as its own Google/Meta ad account (added on request).</t>
         </is>
       </c>
     </row>
@@ -2021,131 +2230,1056 @@
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>We Go Bananas</t>
-        </is>
-      </c>
-      <c r="C25" s="3" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
-      </c>
-      <c r="D25" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E25" s="6" t="n"/>
+          <t>Peppino</t>
+        </is>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>Amsterdam</t>
+        </is>
+      </c>
+      <c r="D25" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E25" s="5" t="inlineStr">
+        <is>
+          <t>Active (via Lavash account)</t>
+        </is>
+      </c>
       <c r="F25" s="6" t="n"/>
-      <c r="G25" s="6" t="n"/>
-      <c r="H25" s="6" t="n"/>
+      <c r="G25" s="7" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/peppinoamsterdamnl/</t>
+        </is>
+      </c>
+      <c r="H25" s="7" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/677550648766246</t>
+        </is>
+      </c>
       <c r="I25" s="6" t="n"/>
       <c r="J25" s="6" t="n"/>
       <c r="K25" s="6" t="n"/>
       <c r="L25" s="6" t="n"/>
-      <c r="M25" s="9" t="n"/>
+      <c r="M25" s="8" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=Peppino+Leidsekruisstraat+32+Amsterdam</t>
+        </is>
+      </c>
       <c r="N25" s="9" t="n"/>
       <c r="O25" s="9" t="n"/>
       <c r="P25" s="9" t="n"/>
-      <c r="Q25" s="5" t="inlineStr">
+      <c r="Q25" s="9" t="n"/>
+      <c r="R25" s="5" t="inlineStr">
+        <is>
+          <t>Found as 'Peppino Amsterdam': its FB page + IG are linked to the Restaurant Lavash Meta ad account (confirmed via Meta). No own website found (listed on TheFork), so Website is left blank. Alt IG found: @peppinoamsterdam. Address: Leidsekruisstraat 30-32, Amsterdam.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" s="4" t="inlineStr">
+        <is>
+          <t>Restaurant ChouChou</t>
+        </is>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D26" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="E26" s="5" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="F26" s="6" t="n"/>
+      <c r="G26" s="7" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/chouchou_scheveningen/</t>
+        </is>
+      </c>
+      <c r="H26" s="7" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/restaurantchouchou/</t>
+        </is>
+      </c>
+      <c r="I26" s="6" t="n"/>
+      <c r="J26" s="6" t="n"/>
+      <c r="K26" s="7" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@chouchou_scheveningen</t>
+        </is>
+      </c>
+      <c r="L26" s="6" t="n"/>
+      <c r="M26" s="8" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=Restaurant+ChouChou+Strandweg+159+Den+Haag</t>
+        </is>
+      </c>
+      <c r="N26" s="9" t="n"/>
+      <c r="O26" s="9" t="n"/>
+      <c r="P26" s="9" t="n"/>
+      <c r="Q26" s="9" t="n"/>
+      <c r="R26" s="5" t="inlineStr">
+        <is>
+          <t>Meta account named 'ChouChou Someho'. FB + IG confirmed via Meta.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" s="4" t="inlineStr">
+        <is>
+          <t>Restaurant De Gouden Wok Zuiderpark</t>
+        </is>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D27" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="E27" s="5" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="F27" s="6" t="n"/>
+      <c r="G27" s="7" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/degoudenwokzuiderpark/</t>
+        </is>
+      </c>
+      <c r="H27" s="7" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/GoudenWok/</t>
+        </is>
+      </c>
+      <c r="I27" s="6" t="n"/>
+      <c r="J27" s="6" t="n"/>
+      <c r="K27" s="7" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@degoudenwok</t>
+        </is>
+      </c>
+      <c r="L27" s="6" t="n"/>
+      <c r="M27" s="8" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=De+Gouden+Wok+Zuiderpark+Den+Haag</t>
+        </is>
+      </c>
+      <c r="N27" s="9" t="n"/>
+      <c r="O27" s="9" t="n"/>
+      <c r="P27" s="9" t="n"/>
+      <c r="Q27" s="9" t="n"/>
+      <c r="R27" s="5" t="inlineStr">
+        <is>
+          <t>FB + IG confirmed via Meta. The same Meta ad account also promotes 'Khlay Zen Thais Massagesalon Rotterdam', which may be a separate client.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="3" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" s="4" t="inlineStr">
+        <is>
+          <t>Restaurant Guru</t>
+        </is>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D28" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="E28" s="5" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="F28" s="6" t="n"/>
+      <c r="G28" s="7" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/guru_amsterdam/</t>
+        </is>
+      </c>
+      <c r="H28" s="7" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/Guruamsterdam/</t>
+        </is>
+      </c>
+      <c r="I28" s="6" t="n"/>
+      <c r="J28" s="6" t="n"/>
+      <c r="K28" s="6" t="n"/>
+      <c r="L28" s="6" t="n"/>
+      <c r="M28" s="8" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=Guru+Restaurant+Rijnstraat+157+Amsterdam</t>
+        </is>
+      </c>
+      <c r="N28" s="9" t="n"/>
+      <c r="O28" s="9" t="n"/>
+      <c r="P28" s="9" t="n"/>
+      <c r="Q28" s="9" t="n"/>
+      <c r="R28" s="5" t="inlineStr">
+        <is>
+          <t>Meta account named 'Guru Indian restaurant'. FB + IG confirmed via Meta.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" s="4" t="inlineStr">
+        <is>
+          <t>Restaurant Lavash</t>
+        </is>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D29" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="E29" s="5" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="F29" s="6" t="n"/>
+      <c r="G29" s="7" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/atlavash/</t>
+        </is>
+      </c>
+      <c r="H29" s="7" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/LavashNL/</t>
+        </is>
+      </c>
+      <c r="I29" s="7" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/restaurant-lavash</t>
+        </is>
+      </c>
+      <c r="J29" s="6" t="n"/>
+      <c r="K29" s="6" t="n"/>
+      <c r="L29" s="6" t="n"/>
+      <c r="M29" s="8" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=Restaurant+Lavash+Korte+Leidsedwarsstraat+119+Amsterdam</t>
+        </is>
+      </c>
+      <c r="N29" s="9" t="n"/>
+      <c r="O29" s="9" t="n"/>
+      <c r="P29" s="9" t="n"/>
+      <c r="Q29" s="9" t="n"/>
+      <c r="R29" s="5" t="inlineStr">
+        <is>
+          <t>FB + IG confirmed via Meta. The same Meta ad account also holds 'Peppino Amsterdam' (FB + IG @peppinoamsterdamnl).</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="3" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" s="4" t="inlineStr">
+        <is>
+          <t>Restaurant MIDO</t>
+        </is>
+      </c>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>Hilversum</t>
+        </is>
+      </c>
+      <c r="D30" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E30" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F30" s="6" t="n"/>
+      <c r="G30" s="7" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/restaurantmido/</t>
+        </is>
+      </c>
+      <c r="H30" s="8" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/restaurantmidozeist/</t>
+        </is>
+      </c>
+      <c r="I30" s="6" t="n"/>
+      <c r="J30" s="6" t="n"/>
+      <c r="K30" s="6" t="n"/>
+      <c r="L30" s="6" t="n"/>
+      <c r="M30" s="8" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=Restaurant+MIDO+Soestdijkerstraatweg+42A+Hilversum</t>
+        </is>
+      </c>
+      <c r="N30" s="9" t="n"/>
+      <c r="O30" s="9" t="n"/>
+      <c r="P30" s="11" t="inlineStr">
+        <is>
+          <t>https://restaurantmido.nl/hilversum/</t>
+        </is>
+      </c>
+      <c r="Q30" s="9" t="n"/>
+      <c r="R30" s="5" t="inlineStr">
+        <is>
+          <t>MIDO branch 3 of 4. Address: Soestdijkerstraatweg 42A, 1213 XD Hilversum (formerly Restaurant Boeddha). Instagram @restaurantmido is shared by all branches. Not found as its own Google/Meta ad account (added on request).</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="3" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" s="4" t="inlineStr">
+        <is>
+          <t>Restaurant MIDO</t>
+        </is>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>Lisse</t>
+        </is>
+      </c>
+      <c r="D31" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E31" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F31" s="6" t="n"/>
+      <c r="G31" s="7" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/restaurantmido/</t>
+        </is>
+      </c>
+      <c r="H31" s="8" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/restaurantmidozeist/</t>
+        </is>
+      </c>
+      <c r="I31" s="6" t="n"/>
+      <c r="J31" s="6" t="n"/>
+      <c r="K31" s="6" t="n"/>
+      <c r="L31" s="6" t="n"/>
+      <c r="M31" s="8" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=MIDO+Heereweg+10+Lisse</t>
+        </is>
+      </c>
+      <c r="N31" s="9" t="n"/>
+      <c r="O31" s="9" t="n"/>
+      <c r="P31" s="11" t="inlineStr">
+        <is>
+          <t>https://restaurantmido.nl/lisse/</t>
+        </is>
+      </c>
+      <c r="Q31" s="9" t="n"/>
+      <c r="R31" s="5" t="inlineStr">
+        <is>
+          <t>MIDO branch 4 of 4. Address: Heereweg 10, 2161 AG Lisse; its email domain is midolisse.nl. Instagram @restaurantmido is shared by all branches. Not found as its own Google/Meta ad account (added on request).</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="3" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" s="4" t="inlineStr">
+        <is>
+          <t>Restaurant MIDO</t>
+        </is>
+      </c>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>Woerden</t>
+        </is>
+      </c>
+      <c r="D32" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E32" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F32" s="6" t="n"/>
+      <c r="G32" s="7" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/restaurantmido/</t>
+        </is>
+      </c>
+      <c r="H32" s="8" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/restaurantmidozeist/</t>
+        </is>
+      </c>
+      <c r="I32" s="6" t="n"/>
+      <c r="J32" s="6" t="n"/>
+      <c r="K32" s="6" t="n"/>
+      <c r="L32" s="6" t="n"/>
+      <c r="M32" s="8" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=Restaurant+MIDO+Woerden</t>
+        </is>
+      </c>
+      <c r="N32" s="9" t="n"/>
+      <c r="O32" s="9" t="n"/>
+      <c r="P32" s="11" t="inlineStr">
+        <is>
+          <t>https://restaurantmido.nl/woerden/</t>
+        </is>
+      </c>
+      <c r="Q32" s="9" t="n"/>
+      <c r="R32" s="5" t="inlineStr">
+        <is>
+          <t>MIDO branch 2 of 4. Instagram @restaurantmido is shared by all branches. Not found as its own Google/Meta ad account (added on request).</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="3" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" s="4" t="inlineStr">
+        <is>
+          <t>Restaurant MIDO</t>
+        </is>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>Zeist</t>
+        </is>
+      </c>
+      <c r="D33" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E33" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F33" s="6" t="n"/>
+      <c r="G33" s="7" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/restaurantmido/</t>
+        </is>
+      </c>
+      <c r="H33" s="7" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/restaurantmidozeist/</t>
+        </is>
+      </c>
+      <c r="I33" s="6" t="n"/>
+      <c r="J33" s="6" t="n"/>
+      <c r="K33" s="6" t="n"/>
+      <c r="L33" s="6" t="n"/>
+      <c r="M33" s="8" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=Restaurant+MIDO+Het+Rond+5+Zeist</t>
+        </is>
+      </c>
+      <c r="N33" s="9" t="n"/>
+      <c r="O33" s="9" t="n"/>
+      <c r="P33" s="11" t="inlineStr">
+        <is>
+          <t>https://restaurantmido.nl/zeist/</t>
+        </is>
+      </c>
+      <c r="Q33" s="9" t="n"/>
+      <c r="R33" s="5" t="inlineStr">
+        <is>
+          <t>MIDO branch 1 of 4. Address: Het Rond 5, 3701 HS Zeist. Instagram @restaurantmido is shared by all branches. Not found as its own Google/Meta ad account (added on request).</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="3" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" s="4" t="inlineStr">
+        <is>
+          <t>SKT (SK Tekenwerk)</t>
+        </is>
+      </c>
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D34" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="E34" s="5" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="F34" s="6" t="n"/>
+      <c r="G34" s="8" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/sktekenwerk/</t>
+        </is>
+      </c>
+      <c r="H34" s="7" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/1061694200366933</t>
+        </is>
+      </c>
+      <c r="I34" s="7" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/snel-kwaliteit-tekenwerk</t>
+        </is>
+      </c>
+      <c r="J34" s="6" t="n"/>
+      <c r="K34" s="6" t="n"/>
+      <c r="L34" s="6" t="n"/>
+      <c r="M34" s="8" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=SK+Tekenwerk</t>
+        </is>
+      </c>
+      <c r="N34" s="9" t="n"/>
+      <c r="O34" s="9" t="n"/>
+      <c r="P34" s="9" t="n"/>
+      <c r="Q34" s="9" t="n"/>
+      <c r="R34" s="5" t="inlineStr">
+        <is>
+          <t>SKT = 'Snel Kwaliteit Tekenwerk' (sktekenwerk.nl). Meta ad account not yet enabled for the Meta MCP; FB page 'SK Tekenwerk' found in the business portfolio.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="3" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" s="4" t="inlineStr">
+        <is>
+          <t>SOMEHO</t>
+        </is>
+      </c>
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D35" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E35" s="5" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="F35" s="6" t="n"/>
+      <c r="G35" s="7" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/someho.nl/</t>
+        </is>
+      </c>
+      <c r="H35" s="7" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/101093459711793</t>
+        </is>
+      </c>
+      <c r="I35" s="6" t="n"/>
+      <c r="J35" s="6" t="n"/>
+      <c r="K35" s="6" t="n"/>
+      <c r="L35" s="6" t="n"/>
+      <c r="M35" s="8" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=SOMEHO+Cruquiuszoom+55+Cruquius</t>
+        </is>
+      </c>
+      <c r="N35" s="9" t="n"/>
+      <c r="O35" s="9" t="n"/>
+      <c r="P35" s="9" t="n"/>
+      <c r="Q35" s="9" t="n"/>
+      <c r="R35" s="5" t="inlineStr">
+        <is>
+          <t>Meta only. Hospitality marketing agency (part of M&amp;A Marketing). Kept as its own client row as requested.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="3" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" s="4" t="inlineStr">
+        <is>
+          <t>Spainora</t>
+        </is>
+      </c>
+      <c r="C36" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D36" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="E36" s="5" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="F36" s="7" t="inlineStr">
+        <is>
+          <t>https://x.com/spainora_com</t>
+        </is>
+      </c>
+      <c r="G36" s="8" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/spainora.official/</t>
+        </is>
+      </c>
+      <c r="H36" s="7" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/spainora/</t>
+        </is>
+      </c>
+      <c r="I36" s="6" t="n"/>
+      <c r="J36" s="6" t="n"/>
+      <c r="K36" s="7" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@spainora</t>
+        </is>
+      </c>
+      <c r="L36" s="7" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/@spainora</t>
+        </is>
+      </c>
+      <c r="M36" s="6" t="n"/>
+      <c r="N36" s="9" t="n"/>
+      <c r="O36" s="9" t="n"/>
+      <c r="P36" s="9" t="n"/>
+      <c r="Q36" s="9" t="n"/>
+      <c r="R36" s="5" t="inlineStr">
+        <is>
+          <t>Online real-estate guide (Arevium Capital B.V.), no physical location, so Google Business is left blank. FB page confirmed via Meta.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="3" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" s="4" t="inlineStr">
+        <is>
+          <t>Sushi Sando</t>
+        </is>
+      </c>
+      <c r="C37" s="5" t="inlineStr">
+        <is>
+          <t>Amsterdam – Market 33</t>
+        </is>
+      </c>
+      <c r="D37" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E37" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F37" s="6" t="n"/>
+      <c r="G37" s="7" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/sushisando.nl/</t>
+        </is>
+      </c>
+      <c r="H37" s="7" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/sushisando.nl/</t>
+        </is>
+      </c>
+      <c r="I37" s="6" t="n"/>
+      <c r="J37" s="6" t="n"/>
+      <c r="K37" s="6" t="n"/>
+      <c r="L37" s="6" t="n"/>
+      <c r="M37" s="8" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=Sushi+Sando+Claude+Debussylaan+33+Amsterdam</t>
+        </is>
+      </c>
+      <c r="N37" s="9" t="n"/>
+      <c r="O37" s="9" t="n"/>
+      <c r="P37" s="11" t="inlineStr">
+        <is>
+          <t>https://sushisando.nl/</t>
+        </is>
+      </c>
+      <c r="Q37" s="9" t="n"/>
+      <c r="R37" s="5" t="inlineStr">
+        <is>
+          <t>Stand at Market 33. Address: Claude Debussylaan 33, Amsterdam. Socials and website are shared by both locations. Not found as its own Google/Meta ad account (added on request).</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="3" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" s="4" t="inlineStr">
+        <is>
+          <t>Sushi Sando</t>
+        </is>
+      </c>
+      <c r="C38" s="5" t="inlineStr">
+        <is>
+          <t>Den Haag – Foodhall Scheveningen</t>
+        </is>
+      </c>
+      <c r="D38" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E38" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F38" s="6" t="n"/>
+      <c r="G38" s="7" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/sushisando.nl/</t>
+        </is>
+      </c>
+      <c r="H38" s="7" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/sushisando.nl/</t>
+        </is>
+      </c>
+      <c r="I38" s="6" t="n"/>
+      <c r="J38" s="6" t="n"/>
+      <c r="K38" s="6" t="n"/>
+      <c r="L38" s="6" t="n"/>
+      <c r="M38" s="8" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=Sushi+Sando+Strandweg+161+Den+Haag</t>
+        </is>
+      </c>
+      <c r="N38" s="9" t="n"/>
+      <c r="O38" s="9" t="n"/>
+      <c r="P38" s="11" t="inlineStr">
+        <is>
+          <t>https://sushisando.nl/</t>
+        </is>
+      </c>
+      <c r="Q38" s="9" t="n"/>
+      <c r="R38" s="5" t="inlineStr">
+        <is>
+          <t>Stand inside Foodhall Scheveningen (an existing client). Address: Strandweg 161, Den Haag. Socials and website are shared by both locations. Not found as its own Google/Meta ad account (added on request).</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="3" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" s="4" t="inlineStr">
+        <is>
+          <t>Tammy Nails Supply</t>
+        </is>
+      </c>
+      <c r="C39" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D39" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="E39" s="5" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="F39" s="6" t="n"/>
+      <c r="G39" s="7" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/tammynailsupply_official/</t>
+        </is>
+      </c>
+      <c r="H39" s="7" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/tammy.supplynail/</t>
+        </is>
+      </c>
+      <c r="I39" s="6" t="n"/>
+      <c r="J39" s="8" t="inlineStr">
+        <is>
+          <t>https://www.pinterest.com/tammynailsupply/</t>
+        </is>
+      </c>
+      <c r="K39" s="6" t="n"/>
+      <c r="L39" s="6" t="n"/>
+      <c r="M39" s="8" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=Tammy+Nails+Supply+Spoorsingel+57+Beverwijk</t>
+        </is>
+      </c>
+      <c r="N39" s="9" t="n"/>
+      <c r="O39" s="9" t="n"/>
+      <c r="P39" s="9" t="n"/>
+      <c r="Q39" s="9" t="n"/>
+      <c r="R39" s="5" t="inlineStr">
+        <is>
+          <t>Meta account named 'Tammy Nails Supply'; FB page 'Tammy Nail Supply'. FB + IG confirmed via Meta. Webshop tammynailsupply.nl.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="3" t="n">
+        <v>39</v>
+      </c>
+      <c r="B40" s="4" t="inlineStr">
+        <is>
+          <t>We Go Bananas</t>
+        </is>
+      </c>
+      <c r="C40" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D40" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="E40" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F40" s="6" t="n"/>
+      <c r="G40" s="6" t="n"/>
+      <c r="H40" s="6" t="n"/>
+      <c r="I40" s="6" t="n"/>
+      <c r="J40" s="6" t="n"/>
+      <c r="K40" s="6" t="n"/>
+      <c r="L40" s="6" t="n"/>
+      <c r="M40" s="6" t="n"/>
+      <c r="N40" s="9" t="n"/>
+      <c r="O40" s="9" t="n"/>
+      <c r="P40" s="9" t="n"/>
+      <c r="Q40" s="9" t="n"/>
+      <c r="R40" s="5" t="inlineStr">
         <is>
           <t>Google Ads only. No matching business or social profiles found online; please confirm what this business is (website/location) and I can re-check.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:Q25"/>
+  <autoFilter ref="A1:R40"/>
   <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G2" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L2" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F3" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G3" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H3" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L3" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F4" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G4" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H4" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L4" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F5" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G5" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H5" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L5" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G6" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H6" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J6" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K6" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L6" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H7" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L7" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F8" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G8" r:id="rId24"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J8" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K8" r:id="rId26"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L8" r:id="rId27"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E9" r:id="rId28"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F9" r:id="rId29"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G9" r:id="rId30"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J9" r:id="rId31"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L9" r:id="rId32"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F10" r:id="rId33"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G10" r:id="rId34"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K10" r:id="rId35"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L10" r:id="rId36"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E11" r:id="rId37"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F11" r:id="rId38"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G11" r:id="rId39"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K11" r:id="rId40"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L11" r:id="rId41"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F12" r:id="rId42"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G12" r:id="rId43"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J12" r:id="rId44"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L12" r:id="rId45"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F13" r:id="rId46"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G13" r:id="rId47"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H13" r:id="rId48"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L13" r:id="rId49"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F14" r:id="rId50"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G14" r:id="rId51"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L14" r:id="rId52"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F15" r:id="rId53"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G15" r:id="rId54"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J15" r:id="rId55"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K15" r:id="rId56"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L15" r:id="rId57"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F16" r:id="rId58"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G16" r:id="rId59"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L16" r:id="rId60"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F17" r:id="rId61"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G17" r:id="rId62"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J17" r:id="rId63"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L17" r:id="rId64"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F18" r:id="rId65"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G18" r:id="rId66"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J18" r:id="rId67"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L18" r:id="rId68"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F19" r:id="rId69"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G19" r:id="rId70"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L19" r:id="rId71"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F20" r:id="rId72"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G20" r:id="rId73"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H20" r:id="rId74"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L20" r:id="rId75"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F21" r:id="rId76"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G21" r:id="rId77"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H21" r:id="rId78"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L21" r:id="rId79"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F22" r:id="rId80"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G22" r:id="rId81"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L22" r:id="rId82"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E23" r:id="rId83"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F23" r:id="rId84"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G23" r:id="rId85"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J23" r:id="rId86"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K23" r:id="rId87"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F24" r:id="rId88"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G24" r:id="rId89"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I24" r:id="rId90"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L24" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H2" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M2" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G3" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H3" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I3" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M3" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G4" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H4" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I4" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M4" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G5" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H5" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I5" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M5" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H6" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I6" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K6" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L6" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M6" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I7" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M7" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G8" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H8" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K8" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L8" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M8" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F9" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G9" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H9" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K9" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M9" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G10" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H10" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L10" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M10" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F11" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G11" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H11" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L11" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M11" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G12" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H12" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K12" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M12" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G13" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M13" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P13" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G14" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H14" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I14" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M14" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G15" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H15" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M15" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G16" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H16" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K16" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L16" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M16" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G17" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H17" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M17" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G19" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H19" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I19" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M19" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P19" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G20" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H20" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I20" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M20" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P20" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G21" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H21" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I21" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M21" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P21" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G22" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H22" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I22" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M22" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P22" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G23" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I23" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M23" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P23" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G24" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I24" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M24" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P24" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G25" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H25" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M25" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G26" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H26" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K26" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M26" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G27" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H27" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K27" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M27" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G28" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H28" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M28" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G29" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H29" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I29" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M29" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G30" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H30" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M30" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P30" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G31" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H31" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M31" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P31" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G32" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H32" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M32" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P32" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G33" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H33" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M33" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P33" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G34" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H34" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I34" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M34" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G35" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H35" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M35" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F36" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G36" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H36" r:id="rId135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K36" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L36" r:id="rId137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G37" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H37" r:id="rId139"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M37" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P37" r:id="rId141"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G38" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H38" r:id="rId143"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M38" r:id="rId144"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P38" r:id="rId145"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G39" r:id="rId146"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H39" r:id="rId147"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J39" r:id="rId148"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M39" r:id="rId149"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
@@ -2158,7 +3292,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B16"/>
+  <dimension ref="A1:B17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -2166,166 +3300,178 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="11" t="inlineStr">
+      <c r="A1" s="12" t="inlineStr">
         <is>
           <t>How to read this sheet</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="12" t="inlineStr">
+      <c r="A2" s="13" t="inlineStr">
         <is>
           <t>Plain blue link</t>
         </is>
       </c>
-      <c r="B2" s="13" t="inlineStr">
+      <c r="B2" s="14" t="inlineStr">
         <is>
           <t>Confirmed via the Meta connector (page/IG linked to the ad account or business portfolio), or an exact name + location match from web search.</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="14" t="inlineStr">
+      <c r="A3" s="15" t="inlineStr">
         <is>
           <t>Orange cell</t>
         </is>
       </c>
-      <c r="B3" s="13" t="inlineStr">
+      <c r="B3" s="14" t="inlineStr">
         <is>
           <t>Found, but not confirmed. Hover the cell to see why. Check it before using.</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="15" t="inlineStr">
+      <c r="A4" s="16" t="inlineStr">
         <is>
           <t>Red status cell</t>
         </is>
       </c>
-      <c r="B4" s="13" t="inlineStr">
+      <c r="B4" s="14" t="inlineStr">
         <is>
           <t>Meta ad account has a problem (Unsettled = unpaid balance; Pending closure).</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="16" t="inlineStr">
+      <c r="A5" s="17" t="inlineStr">
         <is>
           <t>Yellow columns</t>
         </is>
       </c>
-      <c r="B5" s="13" t="inlineStr">
-        <is>
-          <t>For you to fill in manually: Google Drive Link for Assets, Phone Number, Website, Address.</t>
+      <c r="B5" s="14" t="inlineStr">
+        <is>
+          <t>For you to fill in manually: Google Drive Link for Assets, Phone Number, Website, Address. Website is pre-filled only for the clients added on 30 Sep (MIDO, Pad Thai, Sushi Sando, L'albero).</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="12" t="inlineStr">
+      <c r="A6" s="13" t="inlineStr">
+        <is>
+          <t>Branch / Location</t>
+        </is>
+      </c>
+      <c r="B6" s="14" t="inlineStr">
+        <is>
+          <t>Multi-location clients get one row per branch. Shared accounts (e.g. one Instagram for all branches) repeat on each row; branch-specific ones (e.g. Pad Thai's per-branch Facebook pages) differ per row.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="13" t="inlineStr">
         <is>
           <t>Empty social cell</t>
         </is>
       </c>
-      <c r="B6" s="13" t="inlineStr">
+      <c r="B7" s="14" t="inlineStr">
         <is>
           <t>No profile found for that platform.</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="12" t="inlineStr">
+    <row r="8">
+      <c r="A8" s="13" t="inlineStr">
         <is>
           <t>Google Business column</t>
         </is>
       </c>
-      <c r="B7" s="13" t="inlineStr">
+      <c r="B8" s="14" t="inlineStr">
         <is>
           <t>Always a Google Maps search link (a verified Business Profile URL can't be pulled from here). Open it, confirm, and swap in the listing's share link.</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="12" t="inlineStr">
+    <row r="9">
+      <c r="A9" s="13" t="inlineStr">
         <is>
           <t>'—' status</t>
         </is>
       </c>
-      <c r="B8" s="13" t="inlineStr">
+      <c r="B9" s="14" t="inlineStr">
         <is>
           <t>Client has no ad account on that platform.</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="12" t="inlineStr"/>
-    </row>
     <row r="10">
-      <c r="A10" s="11" t="inlineStr">
+      <c r="A10" s="13" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="12" t="inlineStr">
         <is>
           <t>Example format for manual columns</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="17" t="inlineStr">
+    <row r="12">
+      <c r="A12" s="18" t="inlineStr">
         <is>
           <t>Google Drive Link for Assets</t>
         </is>
       </c>
-      <c r="B11" s="13" t="inlineStr">
+      <c r="B12" s="14" t="inlineStr">
         <is>
           <t>https://drive.google.com/drive/folders/...</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="17" t="inlineStr">
+    <row r="13">
+      <c r="A13" s="18" t="inlineStr">
         <is>
           <t>Phone Number</t>
         </is>
       </c>
-      <c r="B12" s="13" t="inlineStr">
+      <c r="B13" s="14" t="inlineStr">
         <is>
           <t>+31 20 123 4567</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="17" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="18" t="inlineStr">
         <is>
           <t>Website</t>
         </is>
       </c>
-      <c r="B13" s="13" t="inlineStr">
+      <c r="B14" s="14" t="inlineStr">
         <is>
           <t>https://www.example.nl</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="17" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="18" t="inlineStr">
         <is>
           <t>Address</t>
         </is>
       </c>
-      <c r="B14" s="13" t="inlineStr">
+      <c r="B15" s="14" t="inlineStr">
         <is>
           <t>Straatnaam 1, 1234 AB Amsterdam</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="12" t="inlineStr"/>
-    </row>
     <row r="16">
-      <c r="A16" s="17" t="inlineStr">
+      <c r="A16" s="13" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="18" t="inlineStr">
         <is>
           <t>Sources</t>
         </is>
       </c>
-      <c r="B16" s="13" t="inlineStr">
-        <is>
-          <t>Google Ads MCC + Meta ad accounts via the Ads MCP connector; Meta pages and IG via the Meta connector; the rest via web search. Compiled 29 Sep 2026.</t>
+      <c r="B17" s="14" t="inlineStr">
+        <is>
+          <t>Google Ads MCC + Meta ad accounts via the Ads MCP connector; Meta pages and IG via the Meta connector; the rest via web search. Compiled 29 Sep 2026; MIDO, Pad Thai, Sushi Sando, L'albero, Peppino and Outstanding Quotes added 30 Sep 2026.</t>
         </is>
       </c>
     </row>
